--- a/output/full_scan/batch_seq8_2026-08-18.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,41 +580,41 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7556</v>
+        <v>7711</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>861.6049084202181</v>
+        <v>901.0611348528756</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>245.5</v>
+        <v>492</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.68120806615201</v>
+        <v>79.65132633583167</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.7498202722391</v>
+        <v>45.02279107179614</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.170321324858409</v>
+        <v>1.20611348528755</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,51 +623,51 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5.364291350214723</v>
+        <v>19.0449536752667</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7714</v>
+        <v>7795</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>837.4279126276439</v>
+        <v>878.9819179154955</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>166</v>
+        <v>572</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>54.58711536722641</v>
+        <v>66.18553149634653</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.83194081669388</v>
+        <v>24.23433106845465</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.695797191717672</v>
+        <v>0.6538196903766845</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.172579446618527</v>
+        <v>20.13834685264402</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7792</v>
+        <v>7556</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>780.4808341262282</v>
+        <v>861.6049084202181</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>252</v>
+        <v>245.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.934505492454</v>
+        <v>59.68120806615201</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.56830096872781</v>
+        <v>25.7498202722391</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.148083412622815</v>
+        <v>1.170321324858409</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,48 +729,48 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>7.957539722804305</v>
+        <v>5.364291350214723</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6936</v>
+        <v>7714</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>742.2997137151048</v>
+        <v>837.4279126276439</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32.35</v>
+        <v>166</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.38193018731684</v>
+        <v>54.58711536722641</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.55292364536406</v>
+        <v>20.83194081669388</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.643090714239916</v>
+        <v>1.695797191717672</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.09277137964192921</v>
+        <v>1.172579446618527</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7751</v>
+        <v>7792</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>727.2499629697126</v>
+        <v>780.4808341262282</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1480</v>
+        <v>252</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.38047383500233</v>
+        <v>62.934505492454</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12.84596487423685</v>
+        <v>29.56830096872781</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.824996296971252</v>
+        <v>1.148083412622815</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,51 +835,51 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>28.71024275306673</v>
+        <v>7.957539722804305</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7805</v>
+        <v>6936</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>716.4064575238531</v>
+        <v>742.2997137151048</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>701</v>
+        <v>32.35</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.00569275228297</v>
+        <v>55.38193018731684</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.80375871533292</v>
+        <v>18.55292364536406</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9403733385325064</v>
+        <v>1.643090714239916</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>11.25823547423387</v>
+        <v>0.09277137964192921</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6967</v>
+        <v>7751</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>702.6174230385179</v>
+        <v>727.2499629697126</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>1480</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.24493833122008</v>
+        <v>59.38047383500233</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.57908595571447</v>
+        <v>12.84596487423685</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.77548407087322</v>
+        <v>2.824996296971252</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4457853267121197</v>
+        <v>28.71024275306673</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7402</v>
+        <v>7805</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>699.7875571518532</v>
+        <v>716.4064575238531</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>118</v>
+        <v>701</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.54339777943228</v>
+        <v>66.00569275228297</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>18.50545799330459</v>
+        <v>30.80375871533292</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.719855259397793</v>
+        <v>0.9403733385325064</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.534320136394538</v>
+        <v>11.25823547423387</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6913</v>
+        <v>6967</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>662.4581173405606</v>
+        <v>702.6174230385179</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>149</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>71.23805762412729</v>
+        <v>60.24493833122008</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.74582150018933</v>
+        <v>14.57908595571447</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6970213754743247</v>
+        <v>4.77548407087322</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.424988928507578</v>
+        <v>0.4457853267121197</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6922</v>
+        <v>7402</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>649.6651549160545</v>
+        <v>699.7875571518532</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.7232836075596</v>
+        <v>58.54339777943228</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21.1433201741342</v>
+        <v>18.50545799330459</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5719120650069303</v>
+        <v>3.719855259397793</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,48 +1100,48 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.230970878212317</v>
+        <v>1.534320136394538</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7750</v>
+        <v>6913</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>644.8525175465513</v>
+        <v>662.4581173405606</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2490</v>
+        <v>149</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.93821482006798</v>
+        <v>71.23805762412729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.86423009265868</v>
+        <v>24.74582150018933</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.584358272866063</v>
+        <v>0.6970213754743247</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>25.29827023819504</v>
+        <v>2.424988928507578</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7744</v>
+        <v>6922</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>627.5707990045897</v>
+        <v>649.6651549160545</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>495</v>
+        <v>200</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.649563525734</v>
+        <v>56.7232836075596</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.70163346559373</v>
+        <v>21.1433201741342</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.821586105353724</v>
+        <v>0.5719120650069303</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,48 +1206,48 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>9.706488006615878</v>
+        <v>2.230970878212317</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, breakout_volume_confirm</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6859</v>
+        <v>7750</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>622.2914668368551</v>
+        <v>644.8525175465513</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>108</v>
+        <v>2490</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.86177243200455</v>
+        <v>61.93821482006798</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.98357803634153</v>
+        <v>18.86423009265868</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.168104173702036</v>
+        <v>2.584358272866063</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,51 +1259,51 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.942288777502282</v>
+        <v>25.29827023819504</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6863</v>
+        <v>7744</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>613.4201658023696</v>
+        <v>627.5707990045897</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>109</v>
+        <v>495</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>41.83070447662386</v>
+        <v>63.649563525734</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.60027988145632</v>
+        <v>22.70163346559373</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4507731269050773</v>
+        <v>1.821586105353724</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-3.359279200286799</v>
+        <v>9.706488006615878</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6903</v>
+        <v>6859</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>607.3357627136771</v>
+        <v>622.2914668368551</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>323.5</v>
+        <v>108</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45.75872107876478</v>
+        <v>55.86177243200455</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.82868699993723</v>
+        <v>24.98357803634153</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8782315776674564</v>
+        <v>1.168104173702036</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2.823524339798912</v>
+        <v>1.942288777502282</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6949</v>
+        <v>6863</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>597.1527076764045</v>
+        <v>613.4201658023696</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1055</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.36101186090345</v>
+        <v>41.83070447662386</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>28.54740510761508</v>
+        <v>33.60027988145632</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8996327246202475</v>
+        <v>0.4507731269050773</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,51 +1418,51 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>12.70177664546749</v>
+        <v>-3.359279200286799</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6933</v>
+        <v>6903</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>584.6702930566055</v>
+        <v>607.3357627136771</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>191.5</v>
+        <v>323.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.67333813399625</v>
+        <v>45.75872107876478</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.3948382074173</v>
+        <v>21.82868699993723</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6981095729771143</v>
+        <v>0.8782315776674564</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.936923260801886</v>
+        <v>2.823524339798912</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8039</v>
+        <v>6949</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>583.9270625748787</v>
+        <v>597.1527076764045</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>277.5</v>
+        <v>1055</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>66.61847193506009</v>
+        <v>62.36101186090345</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.84902795277588</v>
+        <v>28.54740510761508</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.100719917378308</v>
+        <v>0.8996327246202475</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>5.308932589803355</v>
+        <v>12.70177664546749</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7610</v>
+        <v>6933</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>580.725525721321</v>
+        <v>584.6702930566055</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1740</v>
+        <v>191.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.13055832481157</v>
+        <v>61.67333813399625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.52714298136046</v>
+        <v>16.3948382074173</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.524418858931145</v>
+        <v>0.6981095729771143</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>36.84132066146479</v>
+        <v>2.936923260801886</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7788</v>
+        <v>8039</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>572.8772917985704</v>
+        <v>583.9270625748787</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>278</v>
+        <v>277.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.76940221248864</v>
+        <v>66.61847193506009</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.89702769905557</v>
+        <v>30.84902795277588</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.464812236653498</v>
+        <v>1.100719917378308</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,51 +1630,51 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>8.885624897345176</v>
+        <v>5.308932589803355</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7828</v>
+        <v>7610</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>559.4504918594616</v>
+        <v>580.725525721321</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1725</v>
+        <v>1740</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>50.08753641079621</v>
+        <v>48.13055832481157</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.77115629982649</v>
+        <v>20.52714298136046</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6592739070912655</v>
+        <v>1.524418858931145</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,51 +1683,51 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>28.2588358860293</v>
+        <v>36.84132066146479</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6870</v>
+        <v>7788</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>518.4861545538624</v>
+        <v>572.8772917985704</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.54654184210599</v>
+        <v>65.76940221248864</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.25934077396203</v>
+        <v>25.89702769905557</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3966863434275946</v>
+        <v>1.464812236653498</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.308960686432507</v>
+        <v>8.885624897345176</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8042</v>
+        <v>7828</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>511.9216916225462</v>
+        <v>559.4504918594616</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>108.5</v>
+        <v>1725</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>40.9209660280963</v>
+        <v>50.08753641079621</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.12221892580634</v>
+        <v>12.77115629982649</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4372866129320513</v>
+        <v>0.6592739070912655</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
@@ -1789,51 +1789,51 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.161163578907676</v>
+        <v>28.2588358860293</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6914</v>
+        <v>6870</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>509.8096945952204</v>
+        <v>518.4861545538624</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>147.5</v>
+        <v>266</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>58.46940384188493</v>
+        <v>51.54654184210599</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.69247668504664</v>
+        <v>14.25934077396203</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8708555557372832</v>
+        <v>0.3966863434275946</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.028819255085784</v>
+        <v>2.308960686432507</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7704</v>
+        <v>8042</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>507.7856277443252</v>
+        <v>511.9216916225462</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62.9</v>
+        <v>108.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.21281418280044</v>
+        <v>40.9209660280963</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.71595526771322</v>
+        <v>21.12221892580634</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1730245172862822</v>
+        <v>0.4372866129320513</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6980901246725533</v>
+        <v>2.161163578907676</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7631</v>
+        <v>6914</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>498.7317400883097</v>
+        <v>509.8096945952204</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>144.5</v>
+        <v>147.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.23389050887</v>
+        <v>58.46940384188493</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.0474802448826</v>
+        <v>15.69247668504664</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6435992233756408</v>
+        <v>0.8708555557372832</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.482741884625629</v>
+        <v>-0.028819255085784</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1958,38 +1958,38 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8016</v>
+        <v>7704</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>493.2224515368511</v>
+        <v>507.7856277443252</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>288</v>
+        <v>62.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>44.98841149959016</v>
+        <v>58.21281418280044</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.37949964977767</v>
+        <v>22.71595526771322</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.598986131792007</v>
+        <v>0.1730245172862822</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,51 +2001,51 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.369550300474622</v>
+        <v>0.6980901246725533</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7547</v>
+        <v>7631</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>492.599366146224</v>
+        <v>498.7317400883097</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>52</v>
+        <v>144.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.33612084608219</v>
+        <v>56.23389050887</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.12875378439897</v>
+        <v>13.0474802448826</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5927161572827336</v>
+        <v>0.6435992233756408</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7260713724309176</v>
+        <v>1.482741884625629</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8021</v>
+        <v>8016</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>491.635451543411</v>
+        <v>493.2224515368511</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>408.5</v>
+        <v>288</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>47.37133427546792</v>
+        <v>44.98841149959016</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.4262484276977</v>
+        <v>16.37949964977767</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.102022320601586</v>
+        <v>1.598986131792007</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>8.801733105952692</v>
+        <v>1.369550300474622</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,41 +2117,41 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6918</v>
+        <v>7547</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>484.297763794219</v>
+        <v>492.599366146224</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>52</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.04798786234834</v>
+        <v>47.33612084608219</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.94668938029137</v>
+        <v>22.12875378439897</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3308712964188189</v>
+        <v>0.5927161572827336</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.437884277358893</v>
+        <v>0.7260713724309176</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7730</v>
+        <v>8021</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>468.0829887421024</v>
+        <v>491.635451543411</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>157</v>
+        <v>408.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>44.58960878487692</v>
+        <v>47.37133427546792</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.38668333372906</v>
+        <v>14.4262484276977</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.804712817574705</v>
+        <v>2.102022320601586</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,51 +2213,51 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.034587542847102</v>
+        <v>8.801733105952692</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7772</v>
+        <v>6918</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>447.0840170326822</v>
+        <v>484.297763794219</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>93.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.53588988324135</v>
+        <v>59.04798786234834</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.86201057127453</v>
+        <v>22.94668938029137</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5797369747244788</v>
+        <v>0.3308712964188189</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,48 +2266,48 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.209516953259181</v>
+        <v>0.437884277358893</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7747</v>
+        <v>7730</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>437.3814471720974</v>
+        <v>468.0829887421024</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>114.5</v>
+        <v>157</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.20012933768943</v>
+        <v>44.58960878487692</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.69337995475037</v>
+        <v>20.38668333372906</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.433018701999179</v>
+        <v>0.804712817574705</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,51 +2319,51 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>2.22167160531772</v>
+        <v>2.034587542847102</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6937</v>
+        <v>7772</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>433.8493971745474</v>
+        <v>447.0840170326822</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>270</v>
+        <v>93.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.46017895088568</v>
+        <v>42.53588988324135</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.43358627170084</v>
+        <v>24.86201057127453</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5562117962773948</v>
+        <v>0.5797369747244788</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,48 +2372,48 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.365380789431215</v>
+        <v>2.209516953259181</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6944</v>
+        <v>7747</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>427.0344652530884</v>
+        <v>437.3814471720974</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>743</v>
+        <v>114.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40.04961553550776</v>
+        <v>52.20012933768943</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.84443828402868</v>
+        <v>14.69337995475037</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3021738117856398</v>
+        <v>2.433018701999179</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>5.677810506279634</v>
+        <v>2.22167160531772</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6958</v>
+        <v>6937</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>423.1995412926025</v>
+        <v>433.8493971745474</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.4</v>
+        <v>270</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.17339191725122</v>
+        <v>49.46017895088568</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>22.50364839505776</v>
+        <v>11.43358627170084</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6581863582754665</v>
+        <v>0.5562117962773948</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1537905507158624</v>
+        <v>2.365380789431215</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6951</v>
+        <v>6944</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>422.1775199603872</v>
+        <v>427.0344652530884</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>72</v>
+        <v>743</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.11826758410642</v>
+        <v>40.04961553550776</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.15266592108378</v>
+        <v>23.84443828402868</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3949161159125572</v>
+        <v>0.3021738117856398</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,51 +2531,51 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3497280068624704</v>
+        <v>5.677810506279634</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6996</v>
+        <v>6958</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>421.4975189012414</v>
+        <v>423.1995412926025</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>177.5</v>
+        <v>17.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G40" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.0059301606924</v>
+        <v>43.17339191725122</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.78247215035105</v>
+        <v>22.50364839505776</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5726254766384581</v>
+        <v>0.6581863582754665</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7198662490922954</v>
+        <v>-0.1537905507158624</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7769</v>
+        <v>6951</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>420.3541217532895</v>
+        <v>422.1775199603872</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>6525</v>
+        <v>72</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.74119548124197</v>
+        <v>45.11826758410642</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.84607003623259</v>
+        <v>30.15266592108378</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7376734069350988</v>
+        <v>0.3949161159125572</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,51 +2637,51 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>71.52239554844657</v>
+        <v>0.3497280068624704</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7822</v>
+        <v>6996</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>409.8096701963645</v>
+        <v>421.4975189012414</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>897</v>
+        <v>177.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.07615143440456</v>
+        <v>48.0059301606924</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.78616361440684</v>
+        <v>16.78247215035105</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.202594992314052</v>
+        <v>0.5726254766384581</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,51 +2690,51 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>18.22218420682</v>
+        <v>0.7198662490922954</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6910</v>
+        <v>7769</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>406.4555702311239</v>
+        <v>420.3541217532895</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>24.6</v>
+        <v>6525</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.04881916119818</v>
+        <v>51.74119548124197</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.33232496477301</v>
+        <v>10.84607003623259</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.855085765001626</v>
+        <v>0.7376734069350988</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,51 +2743,51 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1209232316569569</v>
+        <v>71.52239554844657</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8040</v>
+        <v>7822</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>404.188124953925</v>
+        <v>409.8096701963645</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>73</v>
+        <v>897</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>43.22810896786197</v>
+        <v>50.07615143440456</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.11347207085602</v>
+        <v>16.78616361440684</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4431493504564921</v>
+        <v>1.202594992314052</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,51 +2796,51 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.37937504755973</v>
+        <v>18.22218420682</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6952</v>
+        <v>6910</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>404.1622782559358</v>
+        <v>406.4555702311239</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>37</v>
+        <v>24.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.99190014301433</v>
+        <v>43.04881916119818</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.16955246931981</v>
+        <v>21.33232496477301</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6532784823478818</v>
+        <v>1.855085765001626</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,51 +2849,51 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0634560933278665</v>
+        <v>0.1209232316569569</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6902</v>
+        <v>8040</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>396.3287897693559</v>
+        <v>404.188124953925</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>133.5</v>
+        <v>73</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>60.11618958294513</v>
+        <v>43.22810896786197</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.29283815917021</v>
+        <v>21.11347207085602</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3624224107041514</v>
+        <v>0.4431493504564921</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.754556489402057</v>
+        <v>1.37937504755973</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6919</v>
+        <v>6952</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>394.4525612915033</v>
+        <v>404.1622782559358</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>104.5</v>
+        <v>37</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.20830796967574</v>
+        <v>51.99190014301433</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.05992494011928</v>
+        <v>25.16955246931981</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6340001749477829</v>
+        <v>0.6532784823478818</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,48 +2955,48 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.4788739158334962</v>
+        <v>0.0634560933278665</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6855</v>
+        <v>6902</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>392.965609363386</v>
+        <v>396.3287897693559</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0</v>
+        <v>133.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>29.88003885729429</v>
+        <v>60.11618958294513</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.718247977805555</v>
+        <v>19.29283815917021</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.02612527132589</v>
+        <v>0.3624224107041514</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-10.85260005325116</v>
+        <v>1.754556489402057</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7768</v>
+        <v>6919</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>391.8008679472952</v>
+        <v>394.4525612915033</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>263.5</v>
+        <v>104.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>41.28131151303986</v>
+        <v>49.20830796967574</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>37.69397004373964</v>
+        <v>15.05992494011928</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5979859726098685</v>
+        <v>0.6340001749477829</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>4.760572006485603</v>
+        <v>-0.4788739158334962</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7810</v>
+        <v>6855</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>391.7346654204993</v>
+        <v>392.965609363386</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>197.5</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.68420026998936</v>
+        <v>29.88003885729429</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.2132346721955</v>
+        <v>9.718247977805555</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7491087747717984</v>
+        <v>0.02612527132589</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.981736308652806</v>
+        <v>-10.85260005325116</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7818</v>
+        <v>7768</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>390.7745679928573</v>
+        <v>391.8008679472952</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>62.4</v>
+        <v>263.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>35.11943405871423</v>
+        <v>41.28131151303986</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.97458642353016</v>
+        <v>37.69397004373964</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3402316072041701</v>
+        <v>0.5979859726098685</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,51 +3167,51 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0035475757899492</v>
+        <v>4.760572006485603</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6931</v>
+        <v>7810</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>389.2898533171236</v>
+        <v>391.7346654204993</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>41.5</v>
+        <v>197.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>59.52345928744069</v>
+        <v>51.68420026998936</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>26.71258437370723</v>
+        <v>18.2132346721955</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7472286253750188</v>
+        <v>0.7491087747717984</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,51 +3220,51 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5482790495376347</v>
+        <v>1.981736308652806</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6971</v>
+        <v>7818</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>383.1989822029944</v>
+        <v>390.7745679928573</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>26.05</v>
+        <v>62.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.17617013051955</v>
+        <v>35.11943405871423</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.08517387979966</v>
+        <v>26.97458642353016</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.594392721810991</v>
+        <v>0.3402316072041701</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0333722466598276</v>
+        <v>0.0035475757899492</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6921</v>
+        <v>6931</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>378.6796973502225</v>
+        <v>389.2898533171236</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>71</v>
+        <v>41.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>59.65749099602033</v>
+        <v>59.52345928744069</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.55861287446952</v>
+        <v>26.71258437370723</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3120819697479087</v>
+        <v>0.7472286253750188</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.43514270516435</v>
+        <v>0.5482790495376347</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7712</v>
+        <v>6971</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>375.0037967240437</v>
+        <v>383.1989822029944</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>144.5</v>
+        <v>26.05</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>47.57544123842824</v>
+        <v>47.17617013051955</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.19660825747875</v>
+        <v>17.08517387979966</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4806381761732086</v>
+        <v>2.594392721810991</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>2</v>
@@ -3379,51 +3379,51 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.313987366653889</v>
+        <v>0.0333722466598276</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7717</v>
+        <v>6921</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>372.1321064645404</v>
+        <v>378.6796973502225</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>425</v>
+        <v>71</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.84421965527275</v>
+        <v>59.65749099602033</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.36495691168689</v>
+        <v>23.55861287446952</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3106634678765305</v>
+        <v>0.3120819697479087</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>7.23046062797124</v>
+        <v>1.43514270516435</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6983</v>
+        <v>7712</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>368.094704144811</v>
+        <v>375.0037967240437</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>297</v>
+        <v>144.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.28900588624821</v>
+        <v>47.57544123842824</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10.13976564015407</v>
+        <v>18.19660825747875</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7342718567088667</v>
+        <v>0.4806381761732086</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.413881319841194</v>
+        <v>2.313987366653889</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6877</v>
+        <v>7717</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>364.0300413372362</v>
+        <v>372.1321064645404</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>122.5</v>
+        <v>425</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.89318390229618</v>
+        <v>47.84421965527275</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.97197654597486</v>
+        <v>19.36495691168689</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.335410042309714</v>
+        <v>0.3106634678765305</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,48 +3538,48 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.197020009214879</v>
+        <v>7.23046062797124</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6861</v>
+        <v>6983</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>361.2777017324044</v>
+        <v>368.094704144811</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>198.5</v>
+        <v>297</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>37.74154608214403</v>
+        <v>38.28900588624821</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>24.19648471129599</v>
+        <v>10.13976564015407</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7878611593580636</v>
+        <v>0.7342718567088667</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>4.893466366056117</v>
+        <v>1.413881319841194</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7820</v>
+        <v>6877</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>358.8375152817049</v>
+        <v>364.0300413372362</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>119</v>
+        <v>122.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>59.07044142859964</v>
+        <v>46.89318390229618</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.30277058032642</v>
+        <v>14.97197654597486</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1787178182719199</v>
+        <v>0.335410042309714</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>2.528726311774298</v>
+        <v>1.197020009214879</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8028</v>
+        <v>6861</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>354.4014172301135</v>
+        <v>361.2777017324044</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>248.5</v>
+        <v>198.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40.55112340113609</v>
+        <v>37.74154608214403</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.13810016957945</v>
+        <v>24.19648471129599</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.563688539890981</v>
+        <v>0.7878611593580636</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0505213473445866</v>
+        <v>4.893466366056117</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6907</v>
+        <v>7820</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>352.6387892512716</v>
+        <v>358.8375152817049</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.87307203175328</v>
+        <v>59.07044142859964</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.7596935643717</v>
+        <v>21.30277058032642</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5843306079129768</v>
+        <v>0.1787178182719199</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.678457843284123</v>
+        <v>2.528726311774298</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8011</v>
+        <v>8028</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>344.5414901946143</v>
+        <v>354.4014172301135</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>15.8</v>
+        <v>248.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.56451852277856</v>
+        <v>40.55112340113609</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>30.44745548179171</v>
+        <v>17.13810016957945</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5457989016216471</v>
+        <v>1.563688539890981</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,51 +3803,51 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0130025878702141</v>
+        <v>-0.0505213473445866</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6869</v>
+        <v>6907</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>344.4305607042098</v>
+        <v>352.6387892512716</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>69.8</v>
+        <v>171</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G64" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.72942885199593</v>
+        <v>45.87307203175328</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.31374731953751</v>
+        <v>16.7596935643717</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.038324764763632</v>
+        <v>0.5843306079129768</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.3155381595869375</v>
+        <v>-2.678457843284123</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7705</v>
+        <v>8011</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>343.9994415548894</v>
+        <v>344.5414901946143</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>30.6</v>
+        <v>15.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.76863106826032</v>
+        <v>38.56451852277856</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.60528090352567</v>
+        <v>30.44745548179171</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2761948151854866</v>
+        <v>0.5457989016216471</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0536109307662914</v>
+        <v>0.0130025878702141</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7827</v>
+        <v>6869</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>325.6331327538343</v>
+        <v>344.4305607042098</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>156</v>
+        <v>69.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.80532682790992</v>
+        <v>53.72942885199593</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.92495158067933</v>
+        <v>16.31374731953751</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.705085228679366</v>
+        <v>2.038324764763632</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.973963600458525</v>
+        <v>0.3155381595869375</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6908</v>
+        <v>7705</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>325.1330849504736</v>
+        <v>343.9994415548894</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>31.4</v>
+        <v>30.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>31.86573915104</v>
+        <v>48.76863106826032</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>31.28611691486513</v>
+        <v>21.60528090352567</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2.113852072631957</v>
+        <v>0.2761948151854866</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0112851091384134</v>
+        <v>0.0536109307662914</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6969</v>
+        <v>7827</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>321.5943753462824</v>
+        <v>325.6331327538343</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>32.2</v>
+        <v>156</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.09301091809397</v>
+        <v>49.80532682790992</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.10480882573896</v>
+        <v>11.92495158067933</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3049875633409629</v>
+        <v>0.705085228679366</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.3643737836002187</v>
+        <v>0.973963600458525</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6906</v>
+        <v>6908</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>321.5268006217665</v>
+        <v>325.1330849504736</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>71.7</v>
+        <v>31.4</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.03081198050173</v>
+        <v>31.86573915104</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.82186725303017</v>
+        <v>31.28611691486513</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2232983547726291</v>
+        <v>2.113852072631957</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.8874318846399825</v>
+        <v>0.0112851091384134</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6901</v>
+        <v>6969</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>313.348219562739</v>
+        <v>321.5943753462824</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>16.55</v>
+        <v>32.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.8525646616728</v>
+        <v>52.09301091809397</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.89663976838209</v>
+        <v>18.10480882573896</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5042950872553645</v>
+        <v>0.3049875633409629</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.049054517976045</v>
+        <v>-0.3643737836002187</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7855</v>
+        <v>6906</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>310.4254758424736</v>
+        <v>321.5268006217665</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>43.55</v>
+        <v>71.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>17.65278364252084</v>
+        <v>44.03081198050173</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>33.34626417652368</v>
+        <v>20.82186725303017</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.242547584247357</v>
+        <v>0.2232983547726291</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-4.721195128670731</v>
+        <v>0.8874318846399825</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7721</v>
+        <v>6901</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>306.7653001190567</v>
+        <v>313.348219562739</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>62</v>
+        <v>16.55</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>44.18676889010147</v>
+        <v>45.8525646616728</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.42102738567353</v>
+        <v>14.89663976838209</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.494760760793308</v>
+        <v>0.5042950872553645</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,51 +4280,51 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.7221023889735283</v>
+        <v>-0.049054517976045</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6953</v>
+        <v>7855</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>303.6246765758704</v>
+        <v>310.4254758424736</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>226</v>
+        <v>43.55</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>54.44871730126996</v>
+        <v>17.65278364252084</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.45814462915039</v>
+        <v>33.34626417652368</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.164006412671522</v>
+        <v>1.242547584247357</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>2.460526809550118</v>
+        <v>-4.721195128670731</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6955</v>
+        <v>7721</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>303.0949880371018</v>
+        <v>306.7653001190567</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.48984293075724</v>
+        <v>44.18676889010147</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8.666424415665002</v>
+        <v>18.42102738567353</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.149147057699413</v>
+        <v>0.494760760793308</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,51 +4386,51 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>3.220637996425912</v>
+        <v>0.7221023889735283</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6962</v>
+        <v>6953</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>302.8991790565566</v>
+        <v>303.6246765758704</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>30.2</v>
+        <v>226</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>38.45690714010654</v>
+        <v>54.44871730126996</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21.64412103846463</v>
+        <v>10.45814462915039</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.839442433374448</v>
+        <v>0.164006412671522</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,51 +4439,51 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.082177888973805</v>
+        <v>2.460526809550118</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7703</v>
+        <v>6955</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>300.6585182340672</v>
+        <v>303.0949880371018</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G76" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.2031614128156</v>
+        <v>51.48984293075724</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.23489959127453</v>
+        <v>8.666424415665002</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6168411601389456</v>
+        <v>1.149147057699413</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>2.076455627653585</v>
+        <v>3.220637996425912</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7722</v>
+        <v>6962</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>299.8378284265507</v>
+        <v>302.8991790565566</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>276</v>
+        <v>30.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.79668265421466</v>
+        <v>38.45690714010654</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.95161236866496</v>
+        <v>21.64412103846463</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5303358342897707</v>
+        <v>0.839442433374448</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,51 +4545,51 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.272575150499784</v>
+        <v>0.082177888973805</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6885</v>
+        <v>7703</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>299.3680190563577</v>
+        <v>300.6585182340672</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>20.45</v>
+        <v>178</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.46452459752525</v>
+        <v>47.2031614128156</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.77342851512679</v>
+        <v>15.23489959127453</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5012530994894254</v>
+        <v>0.6168411601389456</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0025453077371961</v>
+        <v>2.076455627653585</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6887</v>
+        <v>7722</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>298.2901790370845</v>
+        <v>299.8378284265507</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>36.3</v>
+        <v>276</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.52176020070437</v>
+        <v>42.79668265421466</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.22916043300202</v>
+        <v>17.95161236866496</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8969324908811864</v>
+        <v>0.5303358342897707</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,51 +4651,51 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1685572322343853</v>
+        <v>0.272575150499784</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7734</v>
+        <v>6885</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>295.7371569248569</v>
+        <v>299.3680190563577</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>3070</v>
+        <v>20.45</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.81573325656675</v>
+        <v>43.46452459752525</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9.521103500937958</v>
+        <v>10.77342851512679</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5656761525071946</v>
+        <v>0.5012530994894254</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-37.05286113542257</v>
+        <v>0.0025453077371961</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7689</v>
+        <v>6887</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>292.2732261989748</v>
+        <v>298.2901790370845</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>172</v>
+        <v>36.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>30.63039772876613</v>
+        <v>49.52176020070437</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>31.07763033080505</v>
+        <v>16.22916043300202</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.283689763641924</v>
+        <v>0.8969324908811864</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>2.339698880731024</v>
+        <v>-0.1685572322343853</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7715</v>
+        <v>7734</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>292.2066190484905</v>
+        <v>295.7371569248569</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>31.6</v>
+        <v>3070</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.85499629571293</v>
+        <v>44.81573325656675</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.81860297881621</v>
+        <v>9.521103500937958</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2582801661900444</v>
+        <v>0.5656761525071946</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2068277408162916</v>
+        <v>-37.05286113542257</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6957</v>
+        <v>7689</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.6318938864641</v>
+        <v>292.2732261989748</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.73516193429086</v>
+        <v>30.63039772876613</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>18.07065673471092</v>
+        <v>31.07763033080505</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3950378139305699</v>
+        <v>0.283689763641924</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.352207297237165</v>
+        <v>2.339698880731024</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6894</v>
+        <v>7715</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>282.1940964803096</v>
+        <v>292.2066190484905</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>346</v>
+        <v>31.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>53.16798402648178</v>
+        <v>43.85499629571293</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.12970284584783</v>
+        <v>18.81860297881621</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7995941079033497</v>
+        <v>0.2582801661900444</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>2.104837227722535</v>
+        <v>-0.2068277408162916</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6947</v>
+        <v>6957</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>282.1842536758111</v>
+        <v>286.6318938864641</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>214</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.65854774856402</v>
+        <v>47.73516193429086</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.37042026705122</v>
+        <v>18.07065673471092</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3085272216408556</v>
+        <v>0.3950378139305699</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,51 +4969,51 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0163686697498004</v>
+        <v>-1.352207297237165</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6924</v>
+        <v>6894</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>277.640435285948</v>
+        <v>282.1940964803096</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>114</v>
+        <v>346</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G86" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.33568868855676</v>
+        <v>53.16798402648178</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.78105262568298</v>
+        <v>13.12970284584783</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5356110899685681</v>
+        <v>0.7995941079033497</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>1.720577851587776</v>
+        <v>2.104837227722535</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6873</v>
+        <v>6947</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>271.6289280095822</v>
+        <v>282.1842536758111</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>70.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>33.87346401585566</v>
+        <v>39.65854774856402</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.24551982151348</v>
+        <v>15.37042026705122</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.339476208656706</v>
+        <v>0.3085272216408556</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.9455593544742564</v>
+        <v>0.0163686697498004</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6994</v>
+        <v>6924</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>271.3369665339009</v>
+        <v>277.640435285948</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.4</v>
+        <v>114</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>31.06414014522248</v>
+        <v>51.33568868855676</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>37.26386427730144</v>
+        <v>16.78105262568298</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.399416219370827</v>
+        <v>0.5356110899685681</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.3752780357173151</v>
+        <v>1.720577851587776</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6854</v>
+        <v>8033</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>271.0051712347347</v>
+        <v>276.2688321870971</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>89.7</v>
+        <v>186</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>32.97202119445647</v>
+        <v>50.25214845561914</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>35.56556483947631</v>
+        <v>17.95288817197834</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7666191903776168</v>
+        <v>0.2693437782099272</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,51 +5181,51 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.9959882830722028</v>
+        <v>0.6272830894647591</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8038</v>
+        <v>6873</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>266.9151767227945</v>
+        <v>271.6289280095822</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>31.25</v>
+        <v>70.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G90" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>33.8383733275991</v>
+        <v>33.87346401585566</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.26292466214949</v>
+        <v>23.24551982151348</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7750485321398499</v>
+        <v>1.339476208656706</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1249461086763688</v>
+        <v>-0.9455593544742564</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7799</v>
+        <v>6994</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>264.2381737801767</v>
+        <v>271.3369665339009</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>351</v>
+        <v>35.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.08290271215733</v>
+        <v>31.06414014522248</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.22347936752162</v>
+        <v>37.26386427730144</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2914314984904386</v>
+        <v>1.399416219370827</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.2360089448952465</v>
+        <v>0.3752780357173151</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6965</v>
+        <v>6854</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>262.2267561200319</v>
+        <v>271.0051712347347</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>74</v>
+        <v>89.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.08616907225101</v>
+        <v>32.97202119445647</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>32.89765750327216</v>
+        <v>35.56556483947631</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.334984015854433</v>
+        <v>0.7666191903776168</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,51 +5340,51 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.199269106971728</v>
+        <v>0.9959882830722028</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7749</v>
+        <v>8038</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>261.12132661903</v>
+        <v>266.9151767227945</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>327</v>
+        <v>31.25</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G93" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.059643538385</v>
+        <v>33.8383733275991</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>27.75931739771813</v>
+        <v>22.26292466214949</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.288152671766761</v>
+        <v>0.7750485321398499</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,48 +5393,48 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>3.53706936134445</v>
+        <v>0.1249461086763688</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6865</v>
+        <v>7799</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>256.1287481836759</v>
+        <v>264.2381737801767</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G94" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>34.83412577498257</v>
+        <v>41.08290271215733</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.222976108063191</v>
+        <v>18.22347936752162</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.0025739161574789</v>
+        <v>0.2914314984904386</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,48 +5446,48 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.016998144760932</v>
+        <v>-0.2360089448952465</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8032</v>
+        <v>6965</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>254.7841267000348</v>
+        <v>262.2267561200319</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>36.2</v>
+        <v>74</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G95" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.50555519008</v>
+        <v>34.08616907225101</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>23.91103549020746</v>
+        <v>32.89765750327216</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8449259176935545</v>
+        <v>1.334984015854433</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.388390004226808</v>
+        <v>-0.199269106971728</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,38 +5509,38 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7738</v>
+        <v>7749</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>246.7718180632508</v>
+        <v>261.12132661903</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>167</v>
+        <v>327</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G96" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.75867186045856</v>
+        <v>35.059643538385</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33.5273350000562</v>
+        <v>27.75931739771813</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5727885945188897</v>
+        <v>1.288152671766761</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2460863827898097</v>
+        <v>3.53706936134445</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,38 +5562,38 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6909</v>
+        <v>6865</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>239.3966075122455</v>
+        <v>256.1287481836759</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.51318495081858</v>
+        <v>34.83412577498257</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>24.29808549518793</v>
+        <v>9.222976108063191</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5749652639328713</v>
+        <v>0.0025739161574789</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,48 +5605,48 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.4004583170812723</v>
+        <v>-1.016998144760932</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6928</v>
+        <v>8032</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>236.939967120906</v>
+        <v>254.7841267000348</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>48</v>
+        <v>36.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G98" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.41064519859227</v>
+        <v>42.50555519008</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.88196286968049</v>
+        <v>23.91103549020746</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3915699100526624</v>
+        <v>0.8449259176935545</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.021373225583001</v>
+        <v>0.388390004226808</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7842</v>
+        <v>7738</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>236.0028411998992</v>
+        <v>246.7718180632508</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>91.8</v>
+        <v>167</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.8693061338802</v>
+        <v>47.75867186045856</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.75815012858679</v>
+        <v>33.5273350000562</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.479237508452193</v>
+        <v>0.5727885945188897</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>1.762617985313604</v>
+        <v>0.2460863827898097</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7780</v>
+        <v>6909</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>232.4335673926763</v>
+        <v>239.3966075122455</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.89675862927851</v>
+        <v>38.51318495081858</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>33.04679404782046</v>
+        <v>24.29808549518793</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7723630114690146</v>
+        <v>0.5749652639328713</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,48 +5764,48 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0456637915783301</v>
+        <v>0.4004583170812723</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6895</v>
+        <v>6928</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>229.2221921233637</v>
+        <v>236.939967120906</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G101" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>39.3578545193734</v>
+        <v>45.41064519859227</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.412637718825</v>
+        <v>14.88196286968049</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6066099176797077</v>
+        <v>0.3915699100526624</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,51 +5817,51 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.169549531736022</v>
+        <v>0.021373225583001</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7765</v>
+        <v>7842</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>228.5108519625041</v>
+        <v>236.0028411998992</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>223</v>
+        <v>91.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.7826633672662</v>
+        <v>52.8693061338802</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.09219325692082</v>
+        <v>10.75815012858679</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6236159477555557</v>
+        <v>1.479237508452193</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,48 +5870,48 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3065162379088845</v>
+        <v>1.762617985313604</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8024</v>
+        <v>7780</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>226.731953212178</v>
+        <v>232.4335673926763</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>13.35</v>
+        <v>16.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G103" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.52200199074626</v>
+        <v>38.89675862927851</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.51163677029088</v>
+        <v>33.04679404782046</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6932969168432493</v>
+        <v>0.7723630114690146</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,48 +5923,48 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1328469182011091</v>
+        <v>0.0456637915783301</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6862</v>
+        <v>6895</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>222.9644591498233</v>
+        <v>229.2221921233637</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G104" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.75604543175741</v>
+        <v>39.3578545193734</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.0474911411409</v>
+        <v>22.412637718825</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3012815711791503</v>
+        <v>0.6066099176797077</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1.942352750221417</v>
+        <v>1.169549531736022</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7791</v>
+        <v>7765</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>222.808202039732</v>
+        <v>228.5108519625041</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>56.3</v>
+        <v>223</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>17.33621125707559</v>
+        <v>44.7826633672662</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>34.79814314709571</v>
+        <v>17.09219325692082</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3440348313421817</v>
+        <v>0.6236159477555557</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2974900087961585</v>
+        <v>0.3065162379088845</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7728</v>
+        <v>8024</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>216.633332015108</v>
+        <v>226.731953212178</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>597</v>
+        <v>13.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.79677273672477</v>
+        <v>38.52200199074626</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.21430960639452</v>
+        <v>14.51163677029088</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7067445834012449</v>
+        <v>0.6932969168432493</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,48 +6082,48 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>4.523263667512992</v>
+        <v>-0.1328469182011091</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6899</v>
+        <v>6862</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>215.5922033446081</v>
+        <v>222.9644591498233</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>50.5</v>
+        <v>137</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G107" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.80858667643852</v>
+        <v>39.75604543175741</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>19.92113230008005</v>
+        <v>16.0474911411409</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3245917766529441</v>
+        <v>0.3012815711791503</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.3500175717359779</v>
+        <v>1.942352750221417</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6923</v>
+        <v>7791</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>215.0844047387143</v>
+        <v>222.808202039732</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.27792009587125</v>
+        <v>17.33621125707559</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.344820709247337</v>
+        <v>34.79814314709571</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.273074965905015</v>
+        <v>0.3440348313421817</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,51 +6188,51 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.106080313661374</v>
+        <v>-0.2974900087961585</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6916</v>
+        <v>7728</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>206.3488863520616</v>
+        <v>216.633332015108</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.6</v>
+        <v>597</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G109" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.89222809056608</v>
+        <v>45.79677273672477</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.16799101155382</v>
+        <v>18.21430960639452</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.2880688528876686</v>
+        <v>0.7067445834012449</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,48 +6241,48 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1060793766748061</v>
+        <v>4.523263667512992</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7823</v>
+        <v>6899</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>204.1742126868336</v>
+        <v>215.5922033446081</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>83.5</v>
+        <v>50.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G110" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.1779761044621</v>
+        <v>38.80858667643852</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.04320775348825</v>
+        <v>19.92113230008005</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9054087689789638</v>
+        <v>0.3245917766529441</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3459387312534122</v>
+        <v>0.3500175717359779</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,38 +6304,38 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7839</v>
+        <v>6923</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>203.7783644274265</v>
+        <v>215.0844047387143</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>45.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G111" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.48954733935816</v>
+        <v>48.27792009587125</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.00702344331671</v>
+        <v>8.344820709247337</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6915055458744779</v>
+        <v>0.273074965905015</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,51 +6347,51 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2178902435468961</v>
+        <v>0.106080313661374</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6925</v>
+        <v>6916</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>198.1553088778838</v>
+        <v>206.3488863520616</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>50.5</v>
+        <v>18.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G112" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.06759309658244</v>
+        <v>46.89222809056608</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.98722607003517</v>
+        <v>11.16799101155382</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.814736181743724</v>
+        <v>0.2880688528876686</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2445767027018233</v>
+        <v>0.1060793766748061</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7732</v>
+        <v>7823</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>189.7733772707644</v>
+        <v>204.1742126868336</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>33.5</v>
+        <v>83.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.95430720038406</v>
+        <v>50.1779761044621</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3.528604003683941</v>
+        <v>17.04320775348825</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.139129477253483</v>
+        <v>0.9054087689789638</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,48 +6453,48 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.3095477918643814</v>
+        <v>0.3459387312534122</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7821</v>
+        <v>7839</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>185.6957958591341</v>
+        <v>203.7783644274265</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>38.9</v>
+        <v>45.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G114" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.2749268860069</v>
+        <v>48.48954733935816</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.37028778439302</v>
+        <v>17.00702344331671</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.221997427789183</v>
+        <v>0.6915055458744779</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.009582506211742199</v>
+        <v>0.2178902435468961</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8034</v>
+        <v>6925</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>183.479177461574</v>
+        <v>198.1553088778838</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>18.75</v>
+        <v>50.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>36.66891819998719</v>
+        <v>35.06759309658244</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>36.68701938393637</v>
+        <v>13.98722607003517</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3428796448772105</v>
+        <v>1.814736181743724</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>1</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0985062294030141</v>
+        <v>0.2445767027018233</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7803</v>
+        <v>7732</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>166.2997357540139</v>
+        <v>189.7733772707644</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19.1</v>
+        <v>33.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>35.70884243927625</v>
+        <v>46.95430720038406</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.63300175098223</v>
+        <v>3.528604003683941</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5344451469600018</v>
+        <v>1.139129477253483</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0755122402210037</v>
+        <v>-0.3095477918643814</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6890</v>
+        <v>7821</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>163.4970444846325</v>
+        <v>185.6957958591341</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>160.5</v>
+        <v>38.9</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>36.34750976334412</v>
+        <v>36.2749268860069</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12.42463169752417</v>
+        <v>16.37028778439302</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.9445381153709066</v>
+        <v>1.221997427789183</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.4910393649651317</v>
+        <v>-0.009582506211742199</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,41 +6675,41 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7786</v>
+        <v>8034</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>150.7466223252874</v>
+        <v>183.479177461574</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>123</v>
+        <v>18.75</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G118" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.71061928130845</v>
+        <v>36.66891819998719</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.06471465312296</v>
+        <v>36.68701938393637</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7469026835124615</v>
+        <v>0.3428796448772105</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.3186672382002173</v>
+        <v>0.0985062294030141</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7740</v>
+        <v>7803</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>131.8368847289575</v>
+        <v>166.2997357540139</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>141.5</v>
+        <v>19.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.31584454035878</v>
+        <v>35.70884243927625</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>15.51635693119122</v>
+        <v>19.63300175098223</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2805028410250491</v>
+        <v>0.5344451469600018</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.075639509972562</v>
+        <v>0.0755122402210037</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7736</v>
+        <v>6890</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>106.0319809385712</v>
+        <v>163.4970444846325</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>69.5</v>
+        <v>160.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.84666949372545</v>
+        <v>36.34750976334412</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.78347628394151</v>
+        <v>12.42463169752417</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5310135865369769</v>
+        <v>0.9445381153709066</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0613734591733073</v>
+        <v>0.4910393649651317</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,38 +6834,38 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6997</v>
+        <v>7786</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>95.74517405827808</v>
+        <v>150.7466223252874</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G121" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>44.60274820341304</v>
+        <v>44.71061928130845</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.08349625519368</v>
+        <v>13.06471465312296</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0</v>
+        <v>0.7469026835124615</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-2.55863917863972</v>
+        <v>-0.3186672382002173</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6988</v>
+        <v>7740</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>86.19966608291726</v>
+        <v>131.8368847289575</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>12.2</v>
+        <v>141.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.7907207640042</v>
+        <v>43.31584454035878</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.653768531493638</v>
+        <v>15.51635693119122</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7751986058828272</v>
+        <v>0.2805028410250491</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1186725458476426</v>
+        <v>-1.075639509972562</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,38 +6940,38 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7770</v>
+        <v>7736</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>68.86271444380228</v>
+        <v>106.0319809385712</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>38.75</v>
+        <v>69.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G123" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.60510902017206</v>
+        <v>42.84666949372545</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.4156256349885</v>
+        <v>15.78347628394151</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.450856627592426</v>
+        <v>0.5310135865369769</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1.47862411522762</v>
+        <v>0.0613734591733073</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7753</v>
+        <v>6997</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>63.00610326977284</v>
+        <v>95.74517405827808</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>37.2</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>38.82753396772138</v>
+        <v>44.60274820341304</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10.57696546639505</v>
+        <v>11.08349625519368</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.6551079892653852</v>
+        <v>0</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0616164845767379</v>
+        <v>-2.55863917863972</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7760</v>
+        <v>6988</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>59.65233859032166</v>
+        <v>86.19966608291726</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>33</v>
+        <v>12.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>42.80830018403289</v>
+        <v>48.7907207640042</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.20471299069266</v>
+        <v>9.653768531493638</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6059730929069522</v>
+        <v>0.7751986058828272</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0759192234860997</v>
+        <v>0.1186725458476426</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,52 +7099,211 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>君曜</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>68.86271444380228</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>51.60510902017206</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>10.4156256349885</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>1.450856627592426</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>1.47862411522762</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>63.00610326977284</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.82753396772138</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>10.57696546639505</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.6551079892653852</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0616164845767379</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7760</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>享溫馨</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>59.65233859032166</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>42.80830018403289</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>11.20471299069266</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.6059730929069522</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.0759192234860997</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6934</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>心誠鎂</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>56.83322977951833</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>72.3</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>44.50082552182657</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>18.60034839443276</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.755597168153222</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>-0.3857281913792941</v>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
